--- a/Dataset_Demo_3_Cau_Chien_Thuat.xlsx
+++ b/Dataset_Demo_3_Cau_Chien_Thuat.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HoangBuoito i\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A039F06B-B734-459D-8F2C-C545F347E497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6076C6D-E241-4157-AA2F-CD6D876DD17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Set" sheetId="1" r:id="rId1"/>
+    <sheet name="Hướng dẫn" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>STT</t>
   </si>
@@ -36,50 +37,85 @@
     <t>Đáp án chuẩn</t>
   </si>
   <si>
-    <t>Trang</t>
-  </si>
-  <si>
-    <t>Loại câu hỏi</t>
-  </si>
-  <si>
-    <t>Chỉ số MRR trong đánh giá hệ thống QA được tính toán dựa trên công thức nào?</t>
-  </si>
-  <si>
-    <t>Tại sao các mô hình ngôn ngữ lớn đôi khi lại trả lời sai sự thật một cách tự tin?</t>
-  </si>
-  <si>
-    <t>Quy trình bảo trì định kỳ cho dòng máy tính xách tay Dell XPS 13 là gì?</t>
-  </si>
-  <si>
-    <t>Chỉ số MRR (Mean Reciprocal Rank) được tính bằng công thức: $MRR = \frac{1}{|Q|} \sum_{i=1}^{|Q|} \frac{1}{rank_i}$, trong đó $|Q|$ là tổng số câu hỏi và $rank_i$ là vị trí của kết quả đúng đầu tiên.</t>
-  </si>
-  <si>
-    <t>Đây là hiện tượng 'Ảo giác' (Hallucinations). LLM có thể tạo ra nội dung trông có vẻ hợp lý nhưng thực tế là sai hoặc không có căn cứ khi đối mặt với thông tin lạ.</t>
-  </si>
-  <si>
-    <t>Tài liệu không đề cập đến vấn đề này.</t>
-  </si>
-  <si>
-    <t>13, 28</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>BM25 (Từ khóa chuyên môn)</t>
-  </si>
-  <si>
-    <t>Dense (Ngữ nghĩa)</t>
-  </si>
-  <si>
-    <t>Chống ảo giác (Bẫy)</t>
+    <t>Trang_Chuan</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Cột</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>Ví dụ</t>
+  </si>
+  <si>
+    <t>Số thứ tự câu hỏi</t>
+  </si>
+  <si>
+    <t>1, 2, 3</t>
+  </si>
+  <si>
+    <t>Câu hỏi đặt ra cho hệ thống RAG</t>
+  </si>
+  <si>
+    <t>IOB tagging là gì?</t>
+  </si>
+  <si>
+    <t>Ground truth — câu trả lời đúng để so sánh EM/F1</t>
+  </si>
+  <si>
+    <t>IOB tagging là...</t>
+  </si>
+  <si>
+    <t>Số trang tài liệu gốc chứa đáp án (dùng cho MRR)
+Nhiều trang: cách nhau dấu phẩy</t>
+  </si>
+  <si>
+    <t>44
+hoặc 44,45,46</t>
+  </si>
+  <si>
+    <t>Ghi chú nguồn tài liệu (không dùng trong evaluation)</t>
+  </si>
+  <si>
+    <t>Chapter 7 - slide 10</t>
+  </si>
+  <si>
+    <t>Hệ thống Question Answering (QA) được phân loại dựa trên những tiêu chí nào?</t>
+  </si>
+  <si>
+    <t>Chapter 8 - QA Taxonomy (slide 4)</t>
+  </si>
+  <si>
+    <t>Trong đánh giá hệ thống Question Answering, độ đo F1 score được tính toán dựa trên nguyên lý nào?</t>
+  </si>
+  <si>
+    <t>Chapter 8 - Evaluating QA (slide 43)</t>
+  </si>
+  <si>
+    <t>Công thức toán học để tính chỉ số Mean Reciprocal Rank (MRR) trong hệ thống QA được xác định như thế nào?</t>
+  </si>
+  <si>
+    <t>Chapter 8 - Evaluating QA (slide 44)</t>
+  </si>
+  <si>
+    <t>Chỉ số MRR được tính bằng cách lấy trung bình cộng của các nghịch đảo thứ hạng kết quả đúng đầu tiên trên tổng số câu hỏi.</t>
+  </si>
+  <si>
+    <t>Hệ thống QA được phân loại dựa trên hai tiêu chí chính: một là nguồn thông tin mà hệ thống xây dựng trên đó như một đoạn văn, toàn bộ văn bản Web, cơ sở tri thức, bảng dữ liệu, hình ảnh; hai là loại câu hỏi và loại câu trả lời như factoid vs non-factoid, open-domain vs closed-domain.</t>
+  </si>
+  <si>
+    <t>Đối với các câu hỏi có câu trả lời là văn bản tự do, độ đo F1 score được sử dụng để đo lường mức độ trùng lặp token trung bình giữa câu trả lời dự đoán và đáp án chuẩn, xem chúng như một túi các token.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,18 +126,46 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF375623"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -114,16 +178,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFBDD7EE"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFBDD7EE"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFBDD7EE"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFBDD7EE"/>
       </bottom>
       <diagonal/>
     </border>
@@ -131,10 +195,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -196,7 +278,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -228,27 +310,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -280,24 +344,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -477,11 +523,14 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="70.5703125" customWidth="1"/>
-    <col min="3" max="3" width="101.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,58 +547,139 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="4">
+        <v>43</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2">
+        <v>44</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
-        <v>44</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="5" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="6" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>